--- a/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_tax_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -95,6 +95,24 @@
     <t xml:space="preserve">Dothiora prunorum</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycetales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phaffomycetaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces pijperi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_108</t>
   </si>
   <si>
@@ -110,6 +128,15 @@
     <t xml:space="preserve">Ramularia hydrangeae-macrophyllae</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_109</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_112</t>
   </si>
   <si>
@@ -122,6 +149,12 @@
     <t xml:space="preserve">Metschnikowia chrysoperlae</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia nakasei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_123</t>
   </si>
   <si>
@@ -140,9 +173,6 @@
     <t xml:space="preserve">Vishniacozyma</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_127</t>
   </si>
   <si>
@@ -221,6 +251,12 @@
     <t xml:space="preserve">Unknown_165</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma victoriae</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_17</t>
   </si>
   <si>
@@ -233,15 +269,21 @@
     <t xml:space="preserve">Rachicladosporium cboliae</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_179</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_18</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saccharomycetales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saccharomycodaceae</t>
   </si>
   <si>
@@ -257,15 +299,84 @@
     <t xml:space="preserve">Unknown_180</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurotiomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurotiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspergillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penicillium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penicillium bialowiezense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trichomonascaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starmerella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starmerella stellata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leotiomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helotiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachnaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachnum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_214</t>
   </si>
   <si>
     <t xml:space="preserve">Vishniacozyma heimaeyensis</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exobasidiomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microstromatales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_215</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_22</t>
   </si>
   <si>
@@ -278,6 +389,9 @@
     <t xml:space="preserve">Taphrina carpini</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_231</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
@@ -293,6 +407,12 @@
     <t xml:space="preserve">Cladosporium entadae</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma tephrensis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_257</t>
   </si>
   <si>
@@ -308,12 +428,45 @@
     <t xml:space="preserve">Cluster_27</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_272</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_274</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_28</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cystobasidiomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Symmetrosporaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporidiobolales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporidiobolaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporobolomyces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporobolomyces reniformis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_295</t>
   </si>
   <si>
@@ -329,33 +482,12 @@
     <t xml:space="preserve">Cluster_30</t>
   </si>
   <si>
-    <t xml:space="preserve">Eurotiomycetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurotiales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspergillaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillium</t>
-  </si>
-  <si>
     <t xml:space="preserve">Penicillium brevicompactum</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_300</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporidiobolales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporidiobolaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporobolomyces</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sporobolomyces roseus</t>
   </si>
   <si>
@@ -377,12 +509,24 @@
     <t xml:space="preserve">Cluster_33</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_34</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_340</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown_340</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramularia eucalypti</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
@@ -401,15 +545,18 @@
     <t xml:space="preserve">Cluster_38</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_391</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Leotiomycetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helotiales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sclerotiniaceae</t>
   </si>
   <si>
@@ -425,12 +572,36 @@
     <t xml:space="preserve">Podosphaera</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucoromycota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucoromycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucorales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucoraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucor circinelloides</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_423</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown_423</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_44</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_46</t>
   </si>
   <si>
@@ -461,6 +632,12 @@
     <t xml:space="preserve">Cluster_53</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_540</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
@@ -488,6 +665,15 @@
     <t xml:space="preserve">Unknown_6</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ploettnerulaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadophora</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_64</t>
   </si>
   <si>
@@ -521,9 +707,30 @@
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_744</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_769</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascoideales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycopsidaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycopsis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycopsis crataegensis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_8</t>
   </si>
   <si>
@@ -534,6 +741,12 @@
   </si>
   <si>
     <t xml:space="preserve">Aureobasidium pullulans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_81</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_85</t>
@@ -1013,24 +1226,24 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1039,68 +1252,68 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
@@ -1129,12 +1342,12 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1146,47 +1359,47 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -1195,24 +1408,24 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1233,38 +1446,38 @@
         <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1276,21 +1489,21 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1299,50 +1512,50 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1354,21 +1567,21 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1377,50 +1590,50 @@
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1429,45 +1642,45 @@
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
         <v>80</v>
-      </c>
-      <c r="G22" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1706,7 @@
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -1504,27 +1717,27 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -1536,151 +1749,151 @@
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -1689,24 +1902,24 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" t="s">
         <v>59</v>
       </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -1715,24 +1928,24 @@
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -1744,21 +1957,21 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -1784,7 +1997,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -1793,76 +2006,76 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
         <v>52</v>
       </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
-      </c>
       <c r="H36" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="H37" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -1871,102 +2084,102 @@
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F38" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H40" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G41" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -1987,12 +2200,12 @@
         <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2001,76 +2214,76 @@
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="H43" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="H45" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2079,50 +2292,50 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H46" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2143,12 +2356,12 @@
         <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2157,24 +2370,24 @@
         <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -2183,24 +2396,24 @@
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -2209,16 +2422,16 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
         <v>42</v>
@@ -2226,85 +2439,85 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D52" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G52" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H52" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="H53" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
@@ -2316,47 +2529,47 @@
         <v>22</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H55" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>147</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
@@ -2365,50 +2578,50 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F57" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="H57" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="H58" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -2429,56 +2642,56 @@
         <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G60" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
@@ -2486,7 +2699,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -2507,12 +2720,12 @@
         <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -2521,76 +2734,76 @@
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="E63" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="G63" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="H64" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -2611,30 +2824,30 @@
         <v>19</v>
       </c>
       <c r="H66" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B67" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
@@ -2642,59 +2855,59 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="E68" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="F68" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="G68" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="H69" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -2715,12 +2928,12 @@
         <v>19</v>
       </c>
       <c r="H70" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -2729,50 +2942,50 @@
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F71" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E72" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F72" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G72" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H72" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -2781,102 +2994,102 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="F73" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="G73" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="H73" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="F74" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G74" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B75" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G75" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D76" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F76" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="G76" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H76" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -2885,42 +3098,42 @@
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
@@ -2928,33 +3141,33 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="F79" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -2966,16 +3179,796 @@
         <v>22</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>101</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>39</v>
+      </c>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" t="s">
+        <v>204</v>
+      </c>
+      <c r="G81" t="s">
+        <v>204</v>
+      </c>
+      <c r="H81" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>39</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
+      </c>
+      <c r="E83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F83" t="s">
+        <v>207</v>
+      </c>
+      <c r="G83" t="s">
+        <v>207</v>
+      </c>
+      <c r="H83" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>209</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" t="s">
+        <v>39</v>
+      </c>
+      <c r="C86" t="s">
+        <v>39</v>
+      </c>
+      <c r="D86" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" t="s">
+        <v>39</v>
+      </c>
+      <c r="F86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G86" t="s">
+        <v>211</v>
+      </c>
+      <c r="H86" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" t="s">
+        <v>39</v>
+      </c>
+      <c r="E87" t="s">
+        <v>39</v>
+      </c>
+      <c r="F87" t="s">
+        <v>213</v>
+      </c>
+      <c r="G87" t="s">
+        <v>213</v>
+      </c>
+      <c r="H87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" t="s">
+        <v>112</v>
+      </c>
+      <c r="F89" t="s">
+        <v>181</v>
+      </c>
+      <c r="G89" t="s">
+        <v>216</v>
+      </c>
+      <c r="H89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>217</v>
+      </c>
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" t="s">
+        <v>111</v>
+      </c>
+      <c r="E90" t="s">
+        <v>112</v>
+      </c>
+      <c r="F90" t="s">
+        <v>218</v>
+      </c>
+      <c r="G90" t="s">
+        <v>219</v>
+      </c>
+      <c r="H90" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>220</v>
+      </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>221</v>
+      </c>
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F92" t="s">
+        <v>222</v>
+      </c>
+      <c r="G92" t="s">
+        <v>222</v>
+      </c>
+      <c r="H92" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>223</v>
+      </c>
+      <c r="B93" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>225</v>
+      </c>
+      <c r="B94" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" t="s">
+        <v>39</v>
+      </c>
+      <c r="D94" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" t="s">
+        <v>226</v>
+      </c>
+      <c r="G94" t="s">
+        <v>226</v>
+      </c>
+      <c r="H94" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>227</v>
+      </c>
+      <c r="B95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" t="s">
+        <v>28</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" t="s">
+        <v>90</v>
+      </c>
+      <c r="G95" t="s">
+        <v>91</v>
+      </c>
+      <c r="H95" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>228</v>
+      </c>
+      <c r="B96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C96" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" t="s">
+        <v>39</v>
+      </c>
+      <c r="F96" t="s">
+        <v>229</v>
+      </c>
+      <c r="G96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H96" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>230</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>231</v>
+      </c>
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" t="s">
+        <v>39</v>
+      </c>
+      <c r="D98" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" t="s">
+        <v>39</v>
+      </c>
+      <c r="F98" t="s">
+        <v>232</v>
+      </c>
+      <c r="G98" t="s">
+        <v>232</v>
+      </c>
+      <c r="H98" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>233</v>
+      </c>
+      <c r="B99" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>234</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" t="s">
+        <v>235</v>
+      </c>
+      <c r="F100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
+        <v>237</v>
+      </c>
+      <c r="H100" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101" t="s">
+        <v>240</v>
+      </c>
+      <c r="G101" t="s">
+        <v>241</v>
+      </c>
+      <c r="H101" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>243</v>
+      </c>
+      <c r="B102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>111</v>
+      </c>
+      <c r="E102" t="s">
+        <v>39</v>
+      </c>
+      <c r="F102" t="s">
+        <v>244</v>
+      </c>
+      <c r="G102" t="s">
+        <v>244</v>
+      </c>
+      <c r="H102" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>245</v>
+      </c>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>247</v>
+      </c>
+      <c r="B104" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" t="s">
+        <v>39</v>
+      </c>
+      <c r="E104" t="s">
+        <v>39</v>
+      </c>
+      <c r="F104" t="s">
+        <v>248</v>
+      </c>
+      <c r="G104" t="s">
+        <v>248</v>
+      </c>
+      <c r="H104" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>249</v>
+      </c>
+      <c r="B105" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" t="s">
+        <v>39</v>
+      </c>
+      <c r="D105" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F105" t="s">
+        <v>250</v>
+      </c>
+      <c r="G105" t="s">
+        <v>250</v>
+      </c>
+      <c r="H105" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>251</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>252</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>253</v>
+      </c>
+      <c r="B108" t="s">
+        <v>39</v>
+      </c>
+      <c r="C108" t="s">
+        <v>39</v>
+      </c>
+      <c r="D108" t="s">
+        <v>39</v>
+      </c>
+      <c r="E108" t="s">
+        <v>39</v>
+      </c>
+      <c r="F108" t="s">
+        <v>254</v>
+      </c>
+      <c r="G108" t="s">
+        <v>254</v>
+      </c>
+      <c r="H108" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>255</v>
+      </c>
+      <c r="B109" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" t="s">
+        <v>62</v>
+      </c>
+      <c r="F110" t="s">
+        <v>63</v>
+      </c>
+      <c r="G110" t="s">
+        <v>64</v>
+      </c>
+      <c r="H110" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_tax_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -395,7 +395,22 @@
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_240</t>
+    <t xml:space="preserve">Viridiplantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptophyta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnoliopsida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_242</t>
@@ -500,9 +515,6 @@
     <t xml:space="preserve">Cluster_317</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_317</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_32</t>
   </si>
   <si>
@@ -518,9 +530,6 @@
     <t xml:space="preserve">Cluster_340</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_340</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_341</t>
   </si>
   <si>
@@ -536,7 +545,10 @@
     <t xml:space="preserve">Cluster_371</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_371</t>
+    <t xml:space="preserve">Prunus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avium</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_379</t>
@@ -596,7 +608,7 @@
     <t xml:space="preserve">Cluster_423</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_423</t>
+    <t xml:space="preserve">pulcherrima</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_44</t>
@@ -647,15 +659,12 @@
     <t xml:space="preserve">Cluster_576</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_576</t>
+    <t xml:space="preserve">sulcatus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_58</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_59</t>
   </si>
   <si>
@@ -692,25 +701,19 @@
     <t xml:space="preserve">Cluster_68</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_68</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_7</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_72</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_744</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_744</t>
+    <t xml:space="preserve">avinus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_769</t>
@@ -758,15 +761,9 @@
     <t xml:space="preserve">Cluster_87</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_87</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_89</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_89</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
@@ -774,9 +771,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_95</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_96</t>
@@ -2156,22 +2150,22 @@
         <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2205,7 +2199,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2226,12 +2220,12 @@
         <v>64</v>
       </c>
       <c r="H43" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -2252,12 +2246,12 @@
         <v>52</v>
       </c>
       <c r="H44" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -2275,7 +2269,7 @@
         <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
@@ -2283,7 +2277,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2309,7 +2303,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -2335,7 +2329,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2361,7 +2355,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2387,7 +2381,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -2413,7 +2407,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -2439,7 +2433,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
@@ -2448,16 +2442,16 @@
         <v>48</v>
       </c>
       <c r="D52" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>39</v>
       </c>
       <c r="F52" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
@@ -2465,7 +2459,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
@@ -2477,21 +2471,21 @@
         <v>93</v>
       </c>
       <c r="E53" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H53" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -2517,7 +2511,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
@@ -2538,12 +2532,12 @@
         <v>64</v>
       </c>
       <c r="H55" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -2564,12 +2558,12 @@
         <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
@@ -2590,12 +2584,12 @@
         <v>101</v>
       </c>
       <c r="H57" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
@@ -2607,21 +2601,21 @@
         <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F58" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H58" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -2642,30 +2636,30 @@
         <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="G60" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
         <v>39</v>
@@ -2673,7 +2667,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -2699,7 +2693,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -2725,7 +2719,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -2740,10 +2734,10 @@
         <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G63" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H63" t="s">
         <v>39</v>
@@ -2751,25 +2745,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="H64" t="s">
         <v>39</v>
@@ -2777,7 +2771,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
@@ -2798,12 +2792,12 @@
         <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -2829,7 +2823,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
@@ -2855,33 +2849,33 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E68" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F68" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="G68" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H68" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
@@ -2907,7 +2901,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -2933,7 +2927,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -2959,7 +2953,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -2974,10 +2968,10 @@
         <v>39</v>
       </c>
       <c r="F72" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G72" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H72" t="s">
         <v>39</v>
@@ -2985,7 +2979,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -3000,10 +2994,10 @@
         <v>112</v>
       </c>
       <c r="F73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G73" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H73" t="s">
         <v>39</v>
@@ -3011,7 +3005,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
@@ -3026,10 +3020,10 @@
         <v>112</v>
       </c>
       <c r="F74" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G74" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H74" t="s">
         <v>39</v>
@@ -3037,59 +3031,59 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E75" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F75" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G75" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H75" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H76" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -3115,7 +3109,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -3141,7 +3135,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
@@ -3153,21 +3147,21 @@
         <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F79" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G79" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H79" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -3193,7 +3187,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
@@ -3208,10 +3202,10 @@
         <v>39</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G81" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H81" t="s">
         <v>39</v>
@@ -3219,7 +3213,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -3245,7 +3239,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
@@ -3260,10 +3254,10 @@
         <v>39</v>
       </c>
       <c r="F83" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G83" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H83" t="s">
         <v>39</v>
@@ -3271,7 +3265,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
@@ -3297,7 +3291,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B85" t="s">
         <v>9</v>
@@ -3323,51 +3317,51 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E86" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F86" t="s">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="G86" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="H86" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="G87" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="H87" t="s">
         <v>39</v>
@@ -3375,7 +3369,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
@@ -3401,7 +3395,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -3416,10 +3410,10 @@
         <v>112</v>
       </c>
       <c r="F89" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G89" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H89" t="s">
         <v>39</v>
@@ -3427,7 +3421,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -3442,10 +3436,10 @@
         <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G90" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H90" t="s">
         <v>39</v>
@@ -3453,7 +3447,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -3479,7 +3473,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -3494,10 +3488,10 @@
         <v>39</v>
       </c>
       <c r="F92" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G92" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H92" t="s">
         <v>39</v>
@@ -3505,7 +3499,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -3526,30 +3520,30 @@
         <v>19</v>
       </c>
       <c r="H93" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="H94" t="s">
         <v>39</v>
@@ -3557,7 +3551,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -3583,25 +3577,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>229</v>
+        <v>19</v>
       </c>
       <c r="H96" t="s">
         <v>39</v>
@@ -3609,7 +3603,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
@@ -3635,33 +3629,33 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E98" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F98" t="s">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="G98" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="H98" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -3687,7 +3681,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
         <v>9</v>
@@ -3699,21 +3693,21 @@
         <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -3728,18 +3722,18 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B102" t="s">
         <v>9</v>
@@ -3754,10 +3748,10 @@
         <v>39</v>
       </c>
       <c r="F102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H102" t="s">
         <v>39</v>
@@ -3765,7 +3759,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B103" t="s">
         <v>9</v>
@@ -3786,30 +3780,30 @@
         <v>19</v>
       </c>
       <c r="H103" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B104" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="H104" t="s">
         <v>39</v>
@@ -3820,22 +3814,22 @@
         <v>249</v>
       </c>
       <c r="B105" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F105" t="s">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="H105" t="s">
         <v>39</v>
@@ -3843,7 +3837,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B106" t="s">
         <v>9</v>
@@ -3869,7 +3863,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
@@ -3895,33 +3889,33 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F108" t="s">
-        <v>254</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>254</v>
+        <v>19</v>
       </c>
       <c r="H108" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B109" t="s">
         <v>9</v>
@@ -3947,7 +3941,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B110" t="s">
         <v>9</v>
@@ -3968,7 +3962,7 @@
         <v>64</v>
       </c>
       <c r="H110" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
